--- a/resources/report/60/95/Declaration.xlsx
+++ b/resources/report/60/95/Declaration.xlsx
@@ -12,7 +12,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7020"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Declaration" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="42">
   <si>
     <t>Mẫu số: 01/ĐKTĐ-HĐĐT</t>
   </si>
@@ -80,21 +80,6 @@
     <t>Đến ngày</t>
   </si>
   <si>
-    <t>VNPT Certification Authority</t>
-  </si>
-  <si>
-    <t>540101011729C448392D84CA58C94D54</t>
-  </si>
-  <si>
-    <t>18/6/2020</t>
-  </si>
-  <si>
-    <t>19/6/2023</t>
-  </si>
-  <si>
-    <t>Thêm mới</t>
-  </si>
-  <si>
     <t>Chúng tôi cam kết hoàn toàn chịu trách nhiệm trước pháp luật về tính chính xác, trung thực của nội dung nêu trên và thực hiện theo đúng quy định của pháp luật.</t>
   </si>
   <si>
@@ -104,45 +89,9 @@
     <t>NGƯỜI NỘP THUẾ</t>
   </si>
   <si>
-    <t>Cơ quan thuế quản lý: Cục Thuế Tỉnh Đồng Nai</t>
-  </si>
-  <si>
-    <t>Người liên hệ: Trần Thị Hồng Lư</t>
-  </si>
-  <si>
-    <t>Điện thoại liên hệ: 356021636</t>
-  </si>
-  <si>
-    <t>Địa chỉ liên hệ: Phân Khu Công Nghiệp Nhơn Trạch 6A, KCN Nhơn Trạch 6, Xã Long Thọ, huyện nhơn Trạch, Tỉnh Đồng Nai</t>
-  </si>
-  <si>
-    <t>Thư điện tử: honglu@daeyoungvn.com</t>
-  </si>
-  <si>
-    <t>xxxxxxxx</t>
-  </si>
-  <si>
-    <t>XXXXXXXXX</t>
-  </si>
-  <si>
     <t>Hình thức đăng ký (Thêm mới, gia hạn, ngừng sử dụng)</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Được ký bởi: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>CÔNG TY TNHH DAE YOUNG TEXTILE VIỆT NAM</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">       </t>
   </si>
   <si>
@@ -158,9 +107,6 @@
     <t xml:space="preserve">      </t>
   </si>
   <si>
-    <t xml:space="preserve"> Doanh nghiệp nhỏ và vừa khác theo đề nghị của Ủy ban nhân dân tỉnh, thành phố trực thuộc trung ương gửi Bộ Tài chính trừ doanh nghiệp hoạt động tại các khu kinh tế, khu công nghiệp, khu công nghệ cao.</t>
-  </si>
-  <si>
     <t>Chuyển dữ liệu hóa đơn điện tử trực tiếp đến cơ quan thuế (điểm b1, khoản 3, Điều 22 của Nghị định).</t>
   </si>
   <si>
@@ -170,9 +116,6 @@
     <t>Chuyển đầy đủ nội dung từng hóa đơn.</t>
   </si>
   <si>
-    <t xml:space="preserve"> Chuyển theo bảng tổng hợp dữ liệu hóa đơn điện tử (điểm a1, khoản 3, Điều 22 của Nghị định).</t>
-  </si>
-  <si>
     <t>Hóa đơn giá trị gia tăng</t>
   </si>
   <si>
@@ -194,20 +137,26 @@
     <t xml:space="preserve">Tên người nộp thuế: </t>
   </si>
   <si>
-    <t>CÔNG TY TNHH DAE YOUNG TEXTILE VIỆT NAM</t>
-  </si>
-  <si>
     <t>Hóa đơn có mã khởi tạo từ máy tính tiền</t>
   </si>
   <si>
     <t>Hóa đơn khác</t>
+  </si>
+  <si>
+    <t>Doanh nghiệp nhỏ và vừa khác theo đề nghị của Ủy ban nhân dân tỉnh, thành phố trực thuộc trung ương gửi Bộ Tài chính trừ doanh nghiệp hoạt động tại các khu kinh tế, khu công nghiệp, khu công nghệ cao.</t>
+  </si>
+  <si>
+    <t>Chuyển theo bảng tổng hợp dữ liệu hóa đơn điện tử (điểm a1, khoản 3, Điều 22 của Nghị định).</t>
+  </si>
+  <si>
+    <t>Được ký bởi:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,13 +179,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -428,7 +370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -499,12 +441,51 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -532,44 +513,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1304,74 +1255,6 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2044700</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>273050</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>292100</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Picture 8"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="4292600" y="9696450"/>
-          <a:ext cx="514350" cy="342900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1663,9 +1546,9 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -1676,41 +1559,41 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
-      <c r="H2" s="43" t="s">
+      <c r="H2" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
       <c r="K2" s="7"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="10"/>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="10"/>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
       <c r="K4" s="7"/>
     </row>
     <row r="5" spans="1:11" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1729,51 +1612,47 @@
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="10"/>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
       <c r="K6" s="7"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="50"/>
+      <c r="J7" s="50"/>
       <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" s="10"/>
-      <c r="C8" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
       <c r="K8" s="7"/>
     </row>
     <row r="9" spans="1:11" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
-      <c r="B9" s="10"/>
+      <c r="B9" s="24"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -1799,100 +1678,86 @@
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
-      <c r="B11" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
+      <c r="B11" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
       <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
-      <c r="B12" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37">
-        <v>3603731213</v>
-      </c>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="37"/>
+      <c r="B12" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
       <c r="K12" s="7"/>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
-      <c r="B13" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
       <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
-      <c r="B14" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="I14" s="37"/>
-      <c r="J14" s="37"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
       <c r="K14" s="7"/>
     </row>
     <row r="15" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
-      <c r="B15" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="37"/>
-      <c r="J15" s="37"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
       <c r="K15" s="7"/>
     </row>
     <row r="16" spans="1:11" ht="33.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
       <c r="K16" s="7"/>
     </row>
     <row r="17" spans="1:11" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1910,66 +1775,66 @@
     </row>
     <row r="18" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
-      <c r="B18" s="36" t="s">
+      <c r="B18" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="36"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
       <c r="K18" s="7"/>
     </row>
     <row r="19" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="10"/>
       <c r="C19" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
+        <v>22</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
       <c r="K19" s="7"/>
     </row>
     <row r="20" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
       <c r="B20" s="10"/>
       <c r="C20" s="23"/>
-      <c r="D20" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
+      <c r="D20" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
       <c r="K20" s="7"/>
     </row>
     <row r="21" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="10"/>
       <c r="C21" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
+        <v>22</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
       <c r="K21" s="7"/>
     </row>
     <row r="22" spans="1:11" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1987,81 +1852,81 @@
     </row>
     <row r="23" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
-      <c r="B23" s="36" t="s">
+      <c r="B23" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
       <c r="K23" s="7"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="10"/>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="37"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="37"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
       <c r="K24" s="7"/>
     </row>
     <row r="25" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="10"/>
       <c r="C25" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="24"/>
+        <v>22</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
       <c r="K25" s="7"/>
     </row>
     <row r="26" spans="1:11" ht="24.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="10"/>
       <c r="C26" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="D26" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="24"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
       <c r="K26" s="7"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="10"/>
-      <c r="C27" s="37" t="s">
+      <c r="C27" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="37"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="37"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
       <c r="K27" s="7"/>
     </row>
     <row r="28" spans="1:11" ht="3" customHeight="1" x14ac:dyDescent="0.3">
@@ -2081,34 +1946,34 @@
       <c r="A29" s="5"/>
       <c r="B29" s="10"/>
       <c r="C29" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D29" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
+        <v>22</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
       <c r="K29" s="7"/>
     </row>
     <row r="30" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="10"/>
       <c r="C30" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D30" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
-      <c r="J30" s="24"/>
+        <v>26</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
       <c r="K30" s="7"/>
     </row>
     <row r="31" spans="1:11" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2126,51 +1991,51 @@
     </row>
     <row r="32" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
-      <c r="B32" s="36" t="s">
+      <c r="B32" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C32" s="36"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="36"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
       <c r="K32" s="7"/>
     </row>
     <row r="33" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
       <c r="B33" s="10"/>
       <c r="C33" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D33" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25"/>
-      <c r="J33" s="25"/>
+        <v>22</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="27"/>
+      <c r="J33" s="27"/>
       <c r="K33" s="7"/>
     </row>
     <row r="34" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
       <c r="B34" s="10"/>
       <c r="C34" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D34" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
+        <v>26</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="27"/>
+      <c r="J34" s="27"/>
       <c r="K34" s="7"/>
     </row>
     <row r="35" spans="1:11" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2188,119 +2053,119 @@
     </row>
     <row r="36" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
-      <c r="B36" s="36" t="s">
+      <c r="B36" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C36" s="36"/>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="36"/>
-      <c r="I36" s="36"/>
-      <c r="J36" s="36"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="28"/>
       <c r="K36" s="7"/>
     </row>
     <row r="37" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
       <c r="B37" s="10"/>
       <c r="C37" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D37" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="25"/>
-      <c r="J37" s="25"/>
+        <v>22</v>
+      </c>
+      <c r="D37" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="27"/>
+      <c r="J37" s="27"/>
       <c r="K37" s="7"/>
     </row>
     <row r="38" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5"/>
       <c r="B38" s="10"/>
       <c r="C38" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D38" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="25"/>
-      <c r="I38" s="25"/>
-      <c r="J38" s="25"/>
+        <v>22</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="27"/>
+      <c r="J38" s="27"/>
       <c r="K38" s="7"/>
     </row>
     <row r="39" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="5"/>
       <c r="B39" s="10"/>
       <c r="C39" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D39" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="25"/>
-      <c r="J39" s="25"/>
+        <v>22</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="27"/>
+      <c r="J39" s="27"/>
       <c r="K39" s="7"/>
     </row>
     <row r="40" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
       <c r="B40" s="10"/>
       <c r="C40" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D40" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
-      <c r="I40" s="25"/>
-      <c r="J40" s="25"/>
+        <v>22</v>
+      </c>
+      <c r="D40" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
+      <c r="J40" s="27"/>
       <c r="K40" s="7"/>
     </row>
     <row r="41" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="5"/>
       <c r="B41" s="10"/>
       <c r="C41" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D41" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="E41" s="25"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="25"/>
-      <c r="I41" s="25"/>
-      <c r="J41" s="25"/>
+        <v>26</v>
+      </c>
+      <c r="D41" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="27"/>
+      <c r="J41" s="27"/>
       <c r="K41" s="7"/>
     </row>
     <row r="42" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="10"/>
       <c r="C42" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D42" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="25"/>
-      <c r="I42" s="25"/>
-      <c r="J42" s="25"/>
+        <v>22</v>
+      </c>
+      <c r="D42" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
+      <c r="I42" s="27"/>
+      <c r="J42" s="27"/>
       <c r="K42" s="7"/>
     </row>
     <row r="43" spans="1:11" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2318,97 +2183,85 @@
     </row>
     <row r="44" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
-      <c r="B44" s="36" t="s">
+      <c r="B44" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="36"/>
-      <c r="H44" s="36"/>
-      <c r="I44" s="36"/>
-      <c r="J44" s="36"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="28"/>
+      <c r="I44" s="28"/>
+      <c r="J44" s="28"/>
       <c r="K44" s="7"/>
     </row>
     <row r="45" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5"/>
-      <c r="B45" s="38" t="s">
+      <c r="B45" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="C45" s="38"/>
-      <c r="D45" s="26" t="s">
+      <c r="C45" s="35"/>
+      <c r="D45" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="E45" s="27"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="46" t="s">
+      <c r="E45" s="40"/>
+      <c r="F45" s="41"/>
+      <c r="G45" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="H45" s="44" t="s">
+      <c r="H45" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="I45" s="45"/>
-      <c r="J45" s="46" t="s">
-        <v>33</v>
+      <c r="I45" s="32"/>
+      <c r="J45" s="37" t="s">
+        <v>21</v>
       </c>
       <c r="K45" s="7"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
-      <c r="B46" s="38"/>
-      <c r="C46" s="38"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="47"/>
+      <c r="B46" s="35"/>
+      <c r="C46" s="35"/>
+      <c r="D46" s="42"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="44"/>
+      <c r="G46" s="38"/>
       <c r="H46" s="12" t="s">
         <v>16</v>
       </c>
       <c r="I46" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="J46" s="47"/>
+      <c r="J46" s="38"/>
       <c r="K46" s="7"/>
     </row>
     <row r="47" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
-      <c r="B47" s="39">
-        <v>1</v>
-      </c>
-      <c r="C47" s="39"/>
-      <c r="D47" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="E47" s="33"/>
-      <c r="F47" s="34"/>
-      <c r="G47" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H47" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="I47" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="J47" s="14" t="s">
-        <v>22</v>
-      </c>
+      <c r="B47" s="36"/>
+      <c r="C47" s="36"/>
+      <c r="D47" s="45"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="47"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="14"/>
       <c r="K47" s="7"/>
     </row>
     <row r="48" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
-      <c r="B48" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
-      <c r="E48" s="37"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="37"/>
-      <c r="H48" s="37"/>
-      <c r="I48" s="37"/>
-      <c r="J48" s="37"/>
+      <c r="B48" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="30"/>
+      <c r="J48" s="30"/>
       <c r="K48" s="7"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
@@ -2418,12 +2271,12 @@
       <c r="D49" s="10"/>
       <c r="E49" s="10"/>
       <c r="F49" s="10"/>
-      <c r="G49" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="H49" s="35"/>
-      <c r="I49" s="35"/>
-      <c r="J49" s="35"/>
+      <c r="G49" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" s="29"/>
+      <c r="I49" s="29"/>
+      <c r="J49" s="29"/>
       <c r="K49" s="7"/>
     </row>
     <row r="50" spans="1:11" s="17" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2433,12 +2286,12 @@
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
-      <c r="G50" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="H50" s="40"/>
-      <c r="I50" s="40"/>
-      <c r="J50" s="40"/>
+      <c r="G50" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="H50" s="33"/>
+      <c r="I50" s="33"/>
+      <c r="J50" s="33"/>
       <c r="K50" s="16"/>
     </row>
     <row r="51" spans="1:11" s="17" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -2448,10 +2301,10 @@
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="18"/>
-      <c r="I51" s="18"/>
-      <c r="J51" s="6"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
+      <c r="I51" s="29"/>
+      <c r="J51" s="29"/>
       <c r="K51" s="16"/>
     </row>
     <row r="52" spans="1:11" s="17" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2460,45 +2313,45 @@
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="H52" s="41"/>
-      <c r="I52" s="41"/>
-      <c r="J52" s="41"/>
+      <c r="F52" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="G52" s="34"/>
+      <c r="H52" s="34"/>
+      <c r="I52" s="34"/>
+      <c r="J52" s="34"/>
       <c r="K52" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="G49:J49"/>
-    <mergeCell ref="G50:J50"/>
-    <mergeCell ref="G52:J52"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="C6:J6"/>
-    <mergeCell ref="C3:J3"/>
-    <mergeCell ref="C4:J4"/>
-    <mergeCell ref="C24:J24"/>
-    <mergeCell ref="C27:J27"/>
+  <mergeCells count="51">
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="G51:J51"/>
     <mergeCell ref="C8:J8"/>
     <mergeCell ref="H14:J14"/>
     <mergeCell ref="H15:J15"/>
     <mergeCell ref="B13:J13"/>
+    <mergeCell ref="B18:J18"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="C4:J4"/>
+    <mergeCell ref="G50:J50"/>
+    <mergeCell ref="G52:J52"/>
     <mergeCell ref="B48:J48"/>
+    <mergeCell ref="D21:J21"/>
     <mergeCell ref="B45:C46"/>
     <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B16:J16"/>
-    <mergeCell ref="B18:J18"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="B36:J36"/>
-    <mergeCell ref="D33:J33"/>
-    <mergeCell ref="D34:J34"/>
     <mergeCell ref="G45:G46"/>
     <mergeCell ref="J45:J46"/>
+    <mergeCell ref="D42:J42"/>
+    <mergeCell ref="D45:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D39:J39"/>
+    <mergeCell ref="D40:J40"/>
+    <mergeCell ref="D41:J41"/>
+    <mergeCell ref="B44:J44"/>
+    <mergeCell ref="B32:J32"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="D25:J25"/>
     <mergeCell ref="D26:J26"/>
@@ -2509,18 +2362,19 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="E12:J12"/>
     <mergeCell ref="F11:J11"/>
-    <mergeCell ref="D42:J42"/>
-    <mergeCell ref="D45:F46"/>
-    <mergeCell ref="D47:F47"/>
     <mergeCell ref="D19:J19"/>
-    <mergeCell ref="D21:J21"/>
     <mergeCell ref="D20:J20"/>
+    <mergeCell ref="B16:J16"/>
+    <mergeCell ref="C24:J24"/>
+    <mergeCell ref="C27:J27"/>
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="D38:J38"/>
+    <mergeCell ref="D34:J34"/>
+    <mergeCell ref="B36:J36"/>
+    <mergeCell ref="D33:J33"/>
+    <mergeCell ref="G49:J49"/>
+    <mergeCell ref="H45:I45"/>
     <mergeCell ref="D37:J37"/>
-    <mergeCell ref="D38:J38"/>
-    <mergeCell ref="D39:J39"/>
-    <mergeCell ref="D40:J40"/>
-    <mergeCell ref="D41:J41"/>
-    <mergeCell ref="B44:J44"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0" header="0.3" footer="0.3"/>

--- a/resources/report/60/95/Declaration.xlsx
+++ b/resources/report/60/95/Declaration.xlsx
@@ -370,7 +370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -447,20 +447,74 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -468,59 +522,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1546,9 +1549,9 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -1559,41 +1562,41 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
-      <c r="H2" s="49" t="s">
+      <c r="H2" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
       <c r="K2" s="7"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="10"/>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="10"/>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
       <c r="K4" s="7"/>
     </row>
     <row r="5" spans="1:11" ht="9.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1612,42 +1615,42 @@
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="10"/>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
       <c r="K6" s="7"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
-      <c r="J7" s="50"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
       <c r="K7" s="7"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" s="10"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
       <c r="K8" s="7"/>
     </row>
     <row r="9" spans="1:11" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1678,86 +1681,86 @@
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
       <c r="K11" s="7"/>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
       <c r="K12" s="7"/>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
       <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
       <c r="K14" s="7"/>
     </row>
     <row r="15" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
       <c r="K15" s="7"/>
     </row>
     <row r="16" spans="1:11" ht="33.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
       <c r="K16" s="7"/>
     </row>
     <row r="17" spans="1:11" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1775,17 +1778,17 @@
     </row>
     <row r="18" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
       <c r="K18" s="7"/>
     </row>
     <row r="19" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1794,30 +1797,30 @@
       <c r="C19" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="D19" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
       <c r="K19" s="7"/>
     </row>
     <row r="20" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
       <c r="B20" s="10"/>
       <c r="C20" s="23"/>
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="34"/>
       <c r="K20" s="7"/>
     </row>
     <row r="21" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1826,15 +1829,15 @@
       <c r="C21" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="D21" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
       <c r="K21" s="7"/>
     </row>
     <row r="22" spans="1:11" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1852,32 +1855,32 @@
     </row>
     <row r="23" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
       <c r="K23" s="7"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="10"/>
-      <c r="C24" s="30" t="s">
+      <c r="C24" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
       <c r="K24" s="7"/>
     </row>
     <row r="25" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1886,15 +1889,15 @@
       <c r="C25" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D25" s="26" t="s">
+      <c r="D25" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="34"/>
       <c r="K25" s="7"/>
     </row>
     <row r="26" spans="1:11" ht="24.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -1903,30 +1906,30 @@
       <c r="C26" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D26" s="26" t="s">
+      <c r="D26" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="34"/>
       <c r="K26" s="7"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="10"/>
-      <c r="C27" s="30" t="s">
+      <c r="C27" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="30"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
       <c r="K27" s="7"/>
     </row>
     <row r="28" spans="1:11" ht="3" customHeight="1" x14ac:dyDescent="0.3">
@@ -1948,15 +1951,15 @@
       <c r="C29" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D29" s="26" t="s">
+      <c r="D29" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="34"/>
       <c r="K29" s="7"/>
     </row>
     <row r="30" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1965,15 +1968,15 @@
       <c r="C30" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="26" t="s">
+      <c r="D30" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="34"/>
       <c r="K30" s="7"/>
     </row>
     <row r="31" spans="1:11" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1991,17 +1994,17 @@
     </row>
     <row r="32" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
       <c r="K32" s="7"/>
     </row>
     <row r="33" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -2010,15 +2013,15 @@
       <c r="C33" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D33" s="26" t="s">
+      <c r="D33" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="27"/>
-      <c r="J33" s="27"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="39"/>
       <c r="K33" s="7"/>
     </row>
     <row r="34" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -2027,15 +2030,15 @@
       <c r="C34" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="26" t="s">
+      <c r="D34" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="27"/>
-      <c r="J34" s="27"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="39"/>
       <c r="K34" s="7"/>
     </row>
     <row r="35" spans="1:11" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2053,17 +2056,17 @@
     </row>
     <row r="36" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
-      <c r="B36" s="28" t="s">
+      <c r="B36" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="28"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
       <c r="K36" s="7"/>
     </row>
     <row r="37" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -2072,15 +2075,15 @@
       <c r="C37" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D37" s="26" t="s">
+      <c r="D37" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="39"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="39"/>
       <c r="K37" s="7"/>
     </row>
     <row r="38" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -2089,15 +2092,15 @@
       <c r="C38" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D38" s="26" t="s">
+      <c r="D38" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="27"/>
-      <c r="J38" s="27"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="39"/>
+      <c r="J38" s="39"/>
       <c r="K38" s="7"/>
     </row>
     <row r="39" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
@@ -2106,15 +2109,15 @@
       <c r="C39" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D39" s="26" t="s">
+      <c r="D39" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="27"/>
-      <c r="J39" s="27"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="39"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="39"/>
+      <c r="J39" s="39"/>
       <c r="K39" s="7"/>
     </row>
     <row r="40" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -2123,15 +2126,15 @@
       <c r="C40" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D40" s="26" t="s">
+      <c r="D40" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="39"/>
+      <c r="G40" s="39"/>
+      <c r="H40" s="39"/>
+      <c r="I40" s="39"/>
+      <c r="J40" s="39"/>
       <c r="K40" s="7"/>
     </row>
     <row r="41" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
@@ -2140,15 +2143,15 @@
       <c r="C41" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D41" s="26" t="s">
+      <c r="D41" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="27"/>
-      <c r="J41" s="27"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="39"/>
+      <c r="H41" s="39"/>
+      <c r="I41" s="39"/>
+      <c r="J41" s="39"/>
       <c r="K41" s="7"/>
     </row>
     <row r="42" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -2157,15 +2160,15 @@
       <c r="C42" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="D42" s="26" t="s">
+      <c r="D42" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
-      <c r="H42" s="27"/>
-      <c r="I42" s="27"/>
-      <c r="J42" s="27"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="39"/>
+      <c r="G42" s="39"/>
+      <c r="H42" s="39"/>
+      <c r="I42" s="39"/>
+      <c r="J42" s="39"/>
       <c r="K42" s="7"/>
     </row>
     <row r="43" spans="1:11" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2183,17 +2186,17 @@
     </row>
     <row r="44" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
-      <c r="B44" s="28" t="s">
+      <c r="B44" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="28"/>
-      <c r="J44" s="28"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="29"/>
+      <c r="I44" s="29"/>
+      <c r="J44" s="29"/>
       <c r="K44" s="7"/>
     </row>
     <row r="45" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -2202,18 +2205,18 @@
         <v>12</v>
       </c>
       <c r="C45" s="35"/>
-      <c r="D45" s="39" t="s">
+      <c r="D45" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="E45" s="40"/>
-      <c r="F45" s="41"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="42"/>
       <c r="G45" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="H45" s="31" t="s">
+      <c r="H45" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="I45" s="32"/>
+      <c r="I45" s="50"/>
       <c r="J45" s="37" t="s">
         <v>21</v>
       </c>
@@ -2223,9 +2226,9 @@
       <c r="A46" s="5"/>
       <c r="B46" s="35"/>
       <c r="C46" s="35"/>
-      <c r="D46" s="42"/>
-      <c r="E46" s="43"/>
-      <c r="F46" s="44"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="45"/>
       <c r="G46" s="38"/>
       <c r="H46" s="12" t="s">
         <v>16</v>
@@ -2240,9 +2243,9 @@
       <c r="A47" s="5"/>
       <c r="B47" s="36"/>
       <c r="C47" s="36"/>
-      <c r="D47" s="45"/>
-      <c r="E47" s="46"/>
-      <c r="F47" s="47"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="47"/>
+      <c r="F47" s="48"/>
       <c r="G47" s="13"/>
       <c r="H47" s="13"/>
       <c r="I47" s="13"/>
@@ -2251,17 +2254,17 @@
     </row>
     <row r="48" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
-      <c r="B48" s="30" t="s">
+      <c r="B48" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="30"/>
-      <c r="G48" s="30"/>
-      <c r="H48" s="30"/>
-      <c r="I48" s="30"/>
-      <c r="J48" s="30"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="28"/>
+      <c r="J48" s="28"/>
       <c r="K48" s="7"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
@@ -2271,12 +2274,12 @@
       <c r="D49" s="10"/>
       <c r="E49" s="10"/>
       <c r="F49" s="10"/>
-      <c r="G49" s="29" t="s">
+      <c r="G49" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
+      <c r="H49" s="51"/>
+      <c r="I49" s="51"/>
+      <c r="J49" s="51"/>
       <c r="K49" s="7"/>
     </row>
     <row r="50" spans="1:11" s="17" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2286,12 +2289,12 @@
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
-      <c r="G50" s="33" t="s">
+      <c r="G50" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="H50" s="33"/>
-      <c r="I50" s="33"/>
-      <c r="J50" s="33"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="32"/>
       <c r="K50" s="16"/>
     </row>
     <row r="51" spans="1:11" s="17" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
@@ -2301,10 +2304,10 @@
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
-      <c r="G51" s="29"/>
-      <c r="H51" s="29"/>
-      <c r="I51" s="29"/>
-      <c r="J51" s="29"/>
+      <c r="G51" s="27"/>
+      <c r="H51" s="27"/>
+      <c r="I51" s="27"/>
+      <c r="J51" s="27"/>
       <c r="K51" s="16"/>
     </row>
     <row r="52" spans="1:11" s="17" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2316,27 +2319,28 @@
       <c r="F52" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="G52" s="34"/>
-      <c r="H52" s="34"/>
-      <c r="I52" s="34"/>
-      <c r="J52" s="34"/>
+      <c r="G52" s="33"/>
+      <c r="H52" s="33"/>
+      <c r="I52" s="33"/>
+      <c r="J52" s="33"/>
       <c r="K52" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="B7:J7"/>
-    <mergeCell ref="G51:J51"/>
-    <mergeCell ref="C8:J8"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="B18:J18"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="C6:J6"/>
-    <mergeCell ref="C3:J3"/>
-    <mergeCell ref="C4:J4"/>
-    <mergeCell ref="G50:J50"/>
+    <mergeCell ref="G49:J49"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="D37:J37"/>
+    <mergeCell ref="C27:J27"/>
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="D38:J38"/>
+    <mergeCell ref="D34:J34"/>
+    <mergeCell ref="B36:J36"/>
+    <mergeCell ref="D33:J33"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="D19:J19"/>
+    <mergeCell ref="D20:J20"/>
+    <mergeCell ref="B16:J16"/>
+    <mergeCell ref="C24:J24"/>
     <mergeCell ref="G52:J52"/>
     <mergeCell ref="B48:J48"/>
     <mergeCell ref="D21:J21"/>
@@ -2352,8 +2356,21 @@
     <mergeCell ref="D41:J41"/>
     <mergeCell ref="B44:J44"/>
     <mergeCell ref="B32:J32"/>
+    <mergeCell ref="D25:J25"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="C4:J4"/>
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="G51:J51"/>
+    <mergeCell ref="C8:J8"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="B18:J18"/>
+    <mergeCell ref="G50:J50"/>
     <mergeCell ref="B11:E11"/>
-    <mergeCell ref="D25:J25"/>
     <mergeCell ref="D26:J26"/>
     <mergeCell ref="D29:J29"/>
     <mergeCell ref="D30:J30"/>
@@ -2361,20 +2378,6 @@
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="E12:J12"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="D19:J19"/>
-    <mergeCell ref="D20:J20"/>
-    <mergeCell ref="B16:J16"/>
-    <mergeCell ref="C24:J24"/>
-    <mergeCell ref="C27:J27"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="D38:J38"/>
-    <mergeCell ref="D34:J34"/>
-    <mergeCell ref="B36:J36"/>
-    <mergeCell ref="D33:J33"/>
-    <mergeCell ref="G49:J49"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="D37:J37"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0" header="0.3" footer="0.3"/>
@@ -2384,8 +2387,333 @@
   <controls>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <control shapeId="1025" r:id="rId4" name="Control 1">
+        <control shapeId="1038" r:id="rId4" name="Control 14">
           <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>41</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>42</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1038" r:id="rId4" name="Control 14"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1037" r:id="rId6" name="Control 13">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>40</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>41</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1037" r:id="rId6" name="Control 13"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1036" r:id="rId7" name="Control 12">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>39</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>40</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1036" r:id="rId7" name="Control 12"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1035" r:id="rId8" name="Control 11">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>38</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>39</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1035" r:id="rId8" name="Control 11"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1034" r:id="rId9" name="Control 10">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>37</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>38</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1034" r:id="rId9" name="Control 10"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1033" r:id="rId10" name="Control 9">
+          <controlPr defaultSize="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>36</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>37</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1033" r:id="rId10" name="Control 9"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1032" r:id="rId12" name="Control 8">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>34</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1032" r:id="rId12" name="Control 8"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1031" r:id="rId13" name="Control 7">
+          <controlPr defaultSize="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>32</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1031" r:id="rId13" name="Control 7"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1030" r:id="rId14" name="Control 6">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>29</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>30</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1030" r:id="rId14" name="Control 6"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1029" r:id="rId15" name="Control 5">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>28</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>29</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1029" r:id="rId15" name="Control 5"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1028" r:id="rId16" name="Control 4">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>25</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>25</xdr:row>
+                <xdr:rowOff>220980</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1028" r:id="rId16" name="Control 4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1027" r:id="rId17" name="Control 3">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>24</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>24</xdr:row>
+                <xdr:rowOff>220980</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1027" r:id="rId17" name="Control 3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1026" r:id="rId18" name="Control 2">
+          <controlPr defaultSize="0" r:id="rId11">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>20</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>21</xdr:row>
+                <xdr:rowOff>45720</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1026" r:id="rId18" name="Control 2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1025" r:id="rId19" name="Control 1">
+          <controlPr defaultSize="0" r:id="rId11">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>2</xdr:col>
@@ -2404,332 +2732,7 @@
         </control>
       </mc:Choice>
       <mc:Fallback>
-        <control shapeId="1025" r:id="rId4" name="Control 1"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1026" r:id="rId6" name="Control 2">
-          <controlPr defaultSize="0" r:id="rId5">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>20</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>21</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1026" r:id="rId6" name="Control 2"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1027" r:id="rId7" name="Control 3">
-          <controlPr defaultSize="0" r:id="rId8">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>24</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>24</xdr:row>
-                <xdr:rowOff>220980</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1027" r:id="rId7" name="Control 3"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1028" r:id="rId9" name="Control 4">
-          <controlPr defaultSize="0" r:id="rId8">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>25</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>25</xdr:row>
-                <xdr:rowOff>220980</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1028" r:id="rId9" name="Control 4"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1029" r:id="rId10" name="Control 5">
-          <controlPr defaultSize="0" r:id="rId8">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>28</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>29</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1029" r:id="rId10" name="Control 5"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1030" r:id="rId11" name="Control 6">
-          <controlPr defaultSize="0" r:id="rId8">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>29</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>30</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1030" r:id="rId11" name="Control 6"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1031" r:id="rId12" name="Control 7">
-          <controlPr defaultSize="0" r:id="rId5">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>32</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>33</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1031" r:id="rId12" name="Control 7"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1032" r:id="rId13" name="Control 8">
-          <controlPr defaultSize="0" r:id="rId8">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>33</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>34</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1032" r:id="rId13" name="Control 8"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1033" r:id="rId14" name="Control 9">
-          <controlPr defaultSize="0" r:id="rId5">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>36</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>37</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1033" r:id="rId14" name="Control 9"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1034" r:id="rId15" name="Control 10">
-          <controlPr defaultSize="0" r:id="rId8">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>37</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>38</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1034" r:id="rId15" name="Control 10"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1035" r:id="rId16" name="Control 11">
-          <controlPr defaultSize="0" r:id="rId8">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>38</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>39</xdr:row>
-                <xdr:rowOff>38100</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1035" r:id="rId16" name="Control 11"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1036" r:id="rId17" name="Control 12">
-          <controlPr defaultSize="0" r:id="rId8">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>39</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>40</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1036" r:id="rId17" name="Control 12"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1037" r:id="rId18" name="Control 13">
-          <controlPr defaultSize="0" r:id="rId8">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>40</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>41</xdr:row>
-                <xdr:rowOff>38100</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1037" r:id="rId18" name="Control 13"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1038" r:id="rId19" name="Control 14">
-          <controlPr defaultSize="0" r:id="rId8">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>41</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>2</xdr:col>
-                <xdr:colOff>228600</xdr:colOff>
-                <xdr:row>42</xdr:row>
-                <xdr:rowOff>45720</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1038" r:id="rId19" name="Control 14"/>
+        <control shapeId="1025" r:id="rId19" name="Control 1"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </controls>
